--- a/DateBase/orders/Nha Thu_2026-5-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-17.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L47"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -600,10 +600,234 @@
       <c r="A21" t="str">
         <v>3</v>
       </c>
+      <c r="C21" t="str">
+        <v>741_袋鼠爪红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F21" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>83_布拉格_undefined_Gerbera L._10stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="C23" t="str" xml:space="preserve">
+        <v xml:space="preserve">413_风铃花淡紫色_Canterbury Bells
+light purple_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>781_琉璃草蓝色_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>551_铁线莲_Glematis_undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>880_铁线莲浅紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>415_百子莲_Agapanthus_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>506_紫罗兰香槟色_violet champagne_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>563_星芹_Astrantia_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>563_星芹_Astrantia_undefined_1bunch</v>
+      </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>4</v>
+      </c>
+      <c r="C32" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>229_黄蝴蝶_Yellow Butterfly_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>280_杏仁果汁_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>606_康乃馨橙光_orange_undefined_20stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>5</v>
+      </c>
+      <c r="C39" t="str">
+        <v>317_尤加利叶细叶_Eucalyptus Parvifolia_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>104_绣球重瓣紫_Hydrangea Purple D_Hydrangea L._1stem</v>
+      </c>
+      <c r="F40" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>109_绣球国产绿_Hydrangea Colombia Green (local)_Hydrangea L._1stem</v>
+      </c>
+      <c r="F41" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>114_绣球孔雀蓝_Hydrangea Peacoke_Hydrangea L._1stem</v>
+      </c>
+      <c r="F42" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>127_绣球孔雀粉_Hydrangea Peacoke_Hydrangea L._1stem</v>
+      </c>
+      <c r="F43" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>624_多丁白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>623_多丁粉太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>6</v>
+      </c>
+      <c r="C46" t="str">
+        <v>775_海芋黑_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F46" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>745_海芋红_Calla Lily_undefined_1bunch</v>
+      </c>
+      <c r="F47" t="str">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L47"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -658,7 +882,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>040201515405555103020100100501554100</v>
+        <v>040201515405555103020100100501554105151033355105512510555102015151515101033</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-5-17.xlsx
+++ b/DateBase/orders/Nha Thu_2026-5-17.xlsx
@@ -884,6 +884,9 @@
       <c r="G2" t="str">
         <v>040201515405555103020100100501554105151033355105512510555102015151515101033</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
